--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488063_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488063_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5776</v>
+        <v>3.7391</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6321</v>
+        <v>4.113</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9455</v>
+        <v>-0.3739</v>
       </c>
       <c r="G2" t="n">
-        <v>1.375</v>
+        <v>5.2318</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3268</v>
+        <v>2.5114</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0482</v>
+        <v>2.7204</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.148</v>
+        <v>4.7876</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2283</v>
+        <v>2.8992</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0804</v>
+        <v>1.8884</v>
       </c>
       <c r="M2" t="n">
-        <v>1.523</v>
+        <v>0.4442</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5551</v>
+        <v>-0.3879</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9679</v>
+        <v>0.8321</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4008</v>
+        <v>0.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2975</v>
+        <v>0.0322</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1033</v>
+        <v>0.0677</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6036</v>
+        <v>-0.7997</v>
       </c>
       <c r="W2" t="n">
         <v>1.4737</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8701</v>
+        <v>-2.2734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3565</v>
+        <v>3.381</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0112</v>
+        <v>0.573</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6546999999999999</v>
+        <v>2.808</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2318</v>
+        <v>1.3013</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5114</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7204</v>
+        <v>0.7595</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7876</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8992</v>
+        <v>0.7938</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8884</v>
+        <v>-0.0726</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4442</v>
+        <v>0.58</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3879</v>
+        <v>-0.252</v>
       </c>
       <c r="O3" t="n">
         <v>0.8321</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7929</v>
+        <v>0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2827</v>
+        <v>-0.3277</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0696</v>
+        <v>-0.3642</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.213</v>
+        <v>0.0365</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7997</v>
+        <v>1.6145</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2734</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.36</v>
+        <v>2.7695</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0013</v>
+        <v>-0.081</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3587</v>
+        <v>2.8504</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3013</v>
+        <v>1.375</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.3268</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7595</v>
+        <v>1.0482</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7213000000000001</v>
+        <v>-0.148</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7938</v>
+        <v>-0.2283</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0726</v>
+        <v>0.0804</v>
       </c>
       <c r="M4" t="n">
-        <v>0.58</v>
+        <v>1.523</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.252</v>
+        <v>0.5551</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8321</v>
+        <v>0.9679</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3487</v>
+        <v>0.5927</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4156</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4127</v>
+        <v>1.0083</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6145</v>
+        <v>0.6036</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2071</v>
+        <v>1.4737</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4074</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4236</v>
+        <v>1.9777</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2904</v>
+        <v>1.7603</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1333</v>
+        <v>0.2175</v>
       </c>
       <c r="G5" t="n">
         <v>0.3748</v>
@@ -844,13 +844,13 @@
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.634</v>
+        <v>-0.0799</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5395</v>
+        <v>-0.0696</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0945</v>
+        <v>-0.0103</v>
       </c>
       <c r="V5" t="n">
         <v>1.8811</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5313</v>
+        <v>0.3015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0751</v>
+        <v>0.098</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4562</v>
+        <v>0.2035</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5981</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4555</v>
+        <v>0.2257</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0148</v>
+        <v>0.0377</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4407</v>
+        <v>0.188</v>
       </c>
       <c r="V7" t="n">
         <v>1.2775</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3494</v>
+        <v>0.2652</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0422</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3917</v>
+        <v>0.3074</v>
       </c>
       <c r="G8" t="n">
         <v>0.156</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1934</v>
+        <v>0.1092</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2558</v>
+        <v>0.1716</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>A. MATEOS PENA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0921</v>
+        <v>0.2277</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0624</v>
+        <v>0.0174</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1545</v>
+        <v>0.2103</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1358</v>
+        <v>0.3819</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.0256</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1358</v>
+        <v>0.4075</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1358</v>
+        <v>0.3415</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.066</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1358</v>
+        <v>0.4075</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0437</v>
+        <v>-0.1542</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0624</v>
+        <v>-0.0229</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0187</v>
+        <v>-0.1313</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MATEOS PENA</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0416</v>
+        <v>0.1202</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0844</v>
+        <v>-0.0624</v>
       </c>
       <c r="F10" t="n">
-        <v>0.126</v>
+        <v>0.1826</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3819</v>
+        <v>0.1358</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0256</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4075</v>
+        <v>0.1358</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3415</v>
+        <v>0.1358</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.066</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4075</v>
+        <v>0.1358</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3403</v>
+        <v>-0.0156</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1248</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2155</v>
+        <v>0.0468</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4648</v>
+        <v>-1.4888</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2027</v>
+        <v>-2.1587</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6675</v>
+        <v>0.67</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5022</v>
+        <v>-0.0684</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4498</v>
+        <v>-0.2786</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0524</v>
+        <v>0.2102</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5846</v>
+        <v>0.619</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5846</v>
+        <v>0.5788</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9176</v>
+        <v>-0.6873</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8652</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0524</v>
+        <v>0.17</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5947</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1805</v>
+        <v>-3.1716</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2356</v>
+        <v>-0.0349</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3642</v>
+        <v>0.3939</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1286</v>
+        <v>-0.4288</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6036</v>
+        <v>-0.1962</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6958</v>
+        <v>-2.6643</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0569</v>
+        <v>-0.9968</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3611</v>
+        <v>-1.6675</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0684</v>
+        <v>-2.5022</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2786</v>
+        <v>-1.4498</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2102</v>
+        <v>-1.0524</v>
       </c>
       <c r="J12" t="n">
-        <v>0.619</v>
+        <v>-0.5846</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5788</v>
+        <v>-0.5846</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6873</v>
+        <v>-1.9176</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.8652</v>
       </c>
       <c r="O12" t="n">
-        <v>0.17</v>
+        <v>-1.0524</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1893</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1716</v>
+        <v>-2.1805</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2419</v>
+        <v>1.0361</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4957</v>
+        <v>1.1647</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7376</v>
+        <v>-0.1286</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1962</v>
+        <v>-0.6036</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1962</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4976</v>
+        <v>-4.7047</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.479</v>
+        <v>-5.884</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0185</v>
+        <v>1.1793</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2045</v>
+        <v>-5.3704</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3682</v>
+        <v>2.9956</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5726</v>
+        <v>-8.366</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4972</v>
+        <v>-3.9551</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8209</v>
+        <v>3.5115</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3181</v>
+        <v>-7.4665</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2927</v>
+        <v>-1.4153</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5472</v>
+        <v>-0.5158</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2545</v>
+        <v>-0.8995</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1716</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9645</v>
+        <v>-5.1538</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7929</v>
+        <v>2.7751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2405</v>
+        <v>0.0265</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5505</v>
+        <v>-0.0595</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3101</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8811</v>
+        <v>3.0178</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5331</v>
+        <v>3.2843</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4142</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.8025</v>
+        <v>-5.0286</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.9256</v>
+        <v>-4.1505</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1231</v>
+        <v>-0.8782</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.3704</v>
+        <v>-0.2045</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9956</v>
+        <v>1.3682</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.366</v>
+        <v>-1.5726</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.9551</v>
+        <v>-0.4972</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5115</v>
+        <v>0.8209</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.4665</v>
+        <v>-1.3181</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4153</v>
+        <v>0.2927</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5158</v>
+        <v>0.5472</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8995</v>
+        <v>-0.2545</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.3787</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.1538</v>
+        <v>-3.9645</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7751</v>
+        <v>0.7929</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0712</v>
+        <v>0.2285</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1011</v>
+        <v>-0.222</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0299</v>
+        <v>0.4505</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0178</v>
+        <v>-1.8811</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2843</v>
+        <v>0.5331</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2666</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="15">
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8205999999999989</v>
+        <v>-0.1964999999999968</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.5297</v>
+        <v>-5.905900000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>5.709400000000001</v>
+        <v>5.7094</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1210000000000004</v>
+        <v>0.1209999999999981</v>
       </c>
       <c r="H15" t="n">
         <v>8.071100000000001</v>
@@ -1600,7 +1600,7 @@
         <v>2.0943</v>
       </c>
       <c r="K15" t="n">
-        <v>9.621700000000001</v>
+        <v>9.621699999999999</v>
       </c>
       <c r="L15" t="n">
         <v>-7.5273</v>
@@ -1612,10 +1612,10 @@
         <v>-1.5508</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4225000000000003</v>
+        <v>-0.4225000000000002</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.937900000000001</v>
+        <v>-6.9379</v>
       </c>
       <c r="Q15" t="n">
         <v>-20.8135</v>
@@ -1624,13 +1624,13 @@
         <v>13.8756</v>
       </c>
       <c r="S15" t="n">
-        <v>1.082299999999999</v>
+        <v>1.7064</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2741000000000002</v>
+        <v>0.3499</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3566</v>
+        <v>1.3564</v>
       </c>
       <c r="V15" t="n">
         <v>4.9139</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.528499999999999</v>
+        <v>6.4815</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1909</v>
+        <v>3.0516</v>
       </c>
       <c r="F16" t="n">
-        <v>4.3376</v>
+        <v>3.4299</v>
       </c>
       <c r="G16" t="n">
         <v>3.5139</v>
@@ -1702,13 +1702,13 @@
         <v>3.3698</v>
       </c>
       <c r="S16" t="n">
-        <v>4.5841</v>
+        <v>1.5372</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8196</v>
+        <v>0.6803</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7645</v>
+        <v>0.8568</v>
       </c>
       <c r="V16" t="n">
         <v>1.2323</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6976</v>
+        <v>4.994</v>
       </c>
       <c r="E17" t="n">
-        <v>3.718</v>
+        <v>4.0236</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9796</v>
+        <v>0.9704</v>
       </c>
       <c r="G17" t="n">
         <v>2.8642</v>
@@ -1780,13 +1780,13 @@
         <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2423</v>
+        <v>0.0541</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3192</v>
+        <v>-0.0136</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0769</v>
+        <v>0.0677</v>
       </c>
       <c r="V17" t="n">
         <v>0.2917</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5794</v>
+        <v>1.3965</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2673</v>
+        <v>-0.6748</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8466</v>
+        <v>2.0713</v>
       </c>
       <c r="G18" t="n">
         <v>6.6515</v>
@@ -1858,13 +1858,13 @@
         <v>3.3698</v>
       </c>
       <c r="S18" t="n">
-        <v>0.55</v>
+        <v>0.3671</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6647</v>
+        <v>0.2572</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1147</v>
+        <v>0.11</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8559</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7109</v>
+        <v>0.7231</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1968</v>
+        <v>-0.4837</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4859</v>
+        <v>1.2068</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3644</v>
@@ -1936,13 +1936,13 @@
         <v>2.7751</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9506</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1304</v>
+        <v>-0.4173</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8202</v>
+        <v>-0.0993</v>
       </c>
       <c r="V19" t="n">
         <v>-0.171</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7994</v>
+        <v>0.3849</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1468</v>
+        <v>-2.1843</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6526</v>
+        <v>2.5691</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3593</v>
+        <v>-1.1689</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3593</v>
+        <v>-0.0232</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-1.1457</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0404</v>
+        <v>-2.0751</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0404</v>
+        <v>0.0271</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.1022</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3996</v>
+        <v>0.9062</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3996</v>
+        <v>-0.0503</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.9565</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4401</v>
+        <v>0.1662</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1872</v>
+        <v>-0.3935</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2529</v>
+        <v>0.5597</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.309</v>
+        <v>-0.7713</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1011</v>
+        <v>-0.1468</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7921</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1689</v>
+        <v>-0.3593</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0232</v>
+        <v>-0.3593</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1457</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0751</v>
+        <v>0.0404</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0271</v>
+        <v>0.0404</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1022</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9062</v>
+        <v>-0.3996</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0503</v>
+        <v>-0.3996</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9565</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5277</v>
+        <v>-0.412</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3103</v>
+        <v>-0.1872</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2174</v>
+        <v>-0.2249</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4743</v>
+        <v>-3.3422</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3597</v>
+        <v>-3.5978</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1146</v>
+        <v>0.2556</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7415</v>
+        <v>-3.3594</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7874</v>
+        <v>-3.8224</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0459</v>
+        <v>0.4629</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2777</v>
+        <v>-2.5716</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3179</v>
+        <v>-3.2948</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0402</v>
+        <v>0.7232</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4638</v>
+        <v>-0.7879</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4695</v>
+        <v>-0.5276</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0057</v>
+        <v>-0.2602</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2481</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.624</v>
+        <v>-0.4275</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3758</v>
+        <v>0.3367</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8811</v>
+        <v>-1.0813</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5331</v>
+        <v>0.3923</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4142</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6863</v>
+        <v>-3.439</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8016</v>
+        <v>-2.1559</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1152</v>
+        <v>-1.2831</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3594</v>
+        <v>-1.7415</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.8224</v>
+        <v>-1.7874</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4629</v>
+        <v>0.0459</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5716</v>
+        <v>-1.2777</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.2948</v>
+        <v>-1.3179</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7232</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7879</v>
+        <v>-0.4638</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5276</v>
+        <v>-0.4695</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2602</v>
+        <v>0.0057</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1805</v>
+        <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4349</v>
+        <v>-0.2129</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6312</v>
+        <v>-0.4202</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1963</v>
+        <v>0.2074</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0813</v>
+        <v>-1.8811</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3923</v>
+        <v>0.5331</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4737</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7689</v>
+        <v>-4.8485</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8906</v>
+        <v>-3.2981</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8783</v>
+        <v>-1.5505</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5097</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0432</v>
+        <v>-0.1229</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3599</v>
+        <v>-0.0476</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4031</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.056699999999998</v>
+        <v>1.579000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.855000000000001</v>
+        <v>-5.466199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5.911499999999999</v>
+        <v>7.045</v>
       </c>
       <c r="G25" t="n">
         <v>0.5264000000000006</v>
@@ -2404,13 +2404,13 @@
         <v>18.633</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2472</v>
+        <v>0.7694</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3581</v>
+        <v>-0.9693999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6051999999999997</v>
+        <v>1.7388</v>
       </c>
       <c r="V25" t="n">
         <v>-4.6724</v>
